--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3937" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3937" uniqueCount="406">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -657,6 +657,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>SubstanceAdministration.statusCode</t>
@@ -5619,7 +5623,7 @@
         <v>74</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>74</v>
+        <v>209</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>74</v>
@@ -5627,10 +5631,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5656,10 +5660,10 @@
         <v>91</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5690,7 +5694,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>74</v>
@@ -5708,7 +5712,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5728,10 +5732,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5829,10 +5833,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5861,7 +5865,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5873,7 +5877,7 @@
         <v>74</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>74</v>
@@ -5912,7 +5916,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5932,17 +5936,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5964,7 +5968,7 @@
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6015,7 +6019,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6035,17 +6039,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -6067,7 +6071,7 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6118,7 +6122,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6138,17 +6142,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -6170,7 +6174,7 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6221,7 +6225,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6241,17 +6245,17 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>80</v>
@@ -6273,7 +6277,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6324,7 +6328,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6344,10 +6348,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6370,11 +6374,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6425,7 +6429,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6445,10 +6449,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6475,7 +6479,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6526,7 +6530,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6546,17 +6550,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
@@ -6578,7 +6582,7 @@
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6629,7 +6633,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6649,17 +6653,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -6677,11 +6681,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6732,7 +6736,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6752,17 +6756,17 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
@@ -6784,7 +6788,7 @@
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6835,7 +6839,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6855,10 +6859,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6881,13 +6885,13 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6938,7 +6942,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6950,7 +6954,7 @@
         <v>74</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>74</v>
@@ -6958,10 +6962,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6984,7 +6988,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -7017,7 +7021,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -7035,7 +7039,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7055,10 +7059,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7081,7 +7085,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -7134,7 +7138,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7154,10 +7158,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7180,7 +7184,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -7213,25 +7217,25 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7251,10 +7255,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7310,25 +7314,25 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7348,10 +7352,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7374,13 +7378,13 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7431,7 +7435,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7451,10 +7455,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7552,17 +7556,17 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>80</v>
@@ -7584,7 +7588,7 @@
       </c>
       <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7635,7 +7639,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7655,17 +7659,17 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>80</v>
@@ -7683,11 +7687,11 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7738,7 +7742,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7758,17 +7762,17 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>80</v>
@@ -7786,11 +7790,11 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7841,7 +7845,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7861,10 +7865,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7891,12 +7895,12 @@
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
@@ -7922,7 +7926,7 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>74</v>
@@ -7940,7 +7944,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7960,17 +7964,17 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>75</v>
@@ -7988,11 +7992,11 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8043,7 +8047,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -8063,17 +8067,17 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>80</v>
@@ -8091,11 +8095,11 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8146,7 +8150,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8166,17 +8170,17 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>80</v>
@@ -8194,11 +8198,11 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8249,7 +8253,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8269,17 +8273,17 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>75</v>
@@ -8297,11 +8301,11 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8352,7 +8356,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8372,10 +8376,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8398,10 +8402,10 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -8453,7 +8457,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8473,10 +8477,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8574,17 +8578,17 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>80</v>
@@ -8606,7 +8610,7 @@
       </c>
       <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8657,7 +8661,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8677,17 +8681,17 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F70" t="s" s="2">
         <v>80</v>
@@ -8705,11 +8709,11 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8760,7 +8764,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8780,17 +8784,17 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F71" t="s" s="2">
         <v>80</v>
@@ -8808,11 +8812,11 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8863,7 +8867,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8883,10 +8887,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8913,12 +8917,12 @@
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
@@ -8944,7 +8948,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8962,7 +8966,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8982,17 +8986,17 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>75</v>
@@ -9010,11 +9014,11 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9065,7 +9069,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9085,17 +9089,17 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>80</v>
@@ -9113,11 +9117,11 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9168,7 +9172,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9188,17 +9192,17 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>80</v>
@@ -9216,11 +9220,11 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9271,7 +9275,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9291,17 +9295,17 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>75</v>
@@ -9319,11 +9323,11 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9374,7 +9378,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9394,10 +9398,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9420,7 +9424,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9473,7 +9477,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9493,10 +9497,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9519,7 +9523,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9552,25 +9556,25 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9590,10 +9594,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9616,13 +9620,13 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9673,7 +9677,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
@@ -9693,10 +9697,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9794,10 +9798,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9895,10 +9899,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9996,10 +10000,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10097,10 +10101,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10200,10 +10204,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10303,10 +10307,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10406,10 +10410,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10509,10 +10513,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10610,10 +10614,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10647,7 +10651,7 @@
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>74</v>
@@ -10669,7 +10673,7 @@
       </c>
       <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>74</v>
@@ -10687,7 +10691,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10707,10 +10711,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10733,7 +10737,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10786,7 +10790,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
@@ -10806,10 +10810,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10832,7 +10836,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10885,7 +10889,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10905,10 +10909,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10931,7 +10935,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10984,7 +10988,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -11004,10 +11008,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11030,7 +11034,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11083,7 +11087,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11103,10 +11107,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11129,7 +11133,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11182,7 +11186,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11202,10 +11206,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11228,7 +11232,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11281,7 +11285,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11301,10 +11305,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11327,7 +11331,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11380,7 +11384,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11400,10 +11404,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11426,7 +11430,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11479,7 +11483,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11499,10 +11503,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11525,7 +11529,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -11578,7 +11582,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11598,10 +11602,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11624,13 +11628,13 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11681,7 +11685,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11701,10 +11705,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11802,10 +11806,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11903,10 +11907,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12004,10 +12008,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12105,10 +12109,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12208,10 +12212,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12311,10 +12315,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12414,10 +12418,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12517,10 +12521,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12618,10 +12622,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12655,7 +12659,7 @@
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>74</v>
@@ -12677,7 +12681,7 @@
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>74</v>
@@ -12695,7 +12699,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12715,10 +12719,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12741,7 +12745,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12794,7 +12798,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>75</v>
@@ -12814,10 +12818,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12915,10 +12919,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13016,10 +13020,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13117,10 +13121,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13218,10 +13222,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13321,10 +13325,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13424,10 +13428,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13527,10 +13531,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13630,10 +13634,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13731,10 +13735,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13764,7 +13768,7 @@
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
@@ -13790,7 +13794,7 @@
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>74</v>
@@ -13808,7 +13812,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -13828,10 +13832,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13865,7 +13869,7 @@
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>74</v>
@@ -13887,7 +13891,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>74</v>
@@ -13905,7 +13909,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -13925,10 +13929,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13984,7 +13988,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>74</v>
@@ -14002,7 +14006,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14022,10 +14026,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14101,7 +14105,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14121,10 +14125,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14147,7 +14151,7 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -14200,7 +14204,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14220,10 +14224,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14246,7 +14250,7 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -14299,7 +14303,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
